--- a/3_CGE/Game_theory_2024/0_External_data/tms_f_initial_shocks.xlsx
+++ b/3_CGE/Game_theory_2024/0_External_data/tms_f_initial_shocks.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\runGTAP375\Game_theory_2024\0_External_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F27E8F8-217C-4E0A-9AB9-4BA3458DC249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4150E23-ECC5-48DC-9D0B-191D51EF585E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10960" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{1BE1B400-F79A-4081-9485-F0F2366A7D5A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1BE1B400-F79A-4081-9485-F0F2366A7D5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Country</t>
   </si>
@@ -83,9 +86,6 @@
     <t xml:space="preserve">colombia   </t>
   </si>
   <si>
-    <t xml:space="preserve">angdrc     </t>
-  </si>
-  <si>
     <t xml:space="preserve">ghana      </t>
   </si>
   <si>
@@ -99,6 +99,18 @@
   </si>
   <si>
     <t xml:space="preserve">peru       </t>
+  </si>
+  <si>
+    <t>drc</t>
+  </si>
+  <si>
+    <t>angola</t>
+  </si>
+  <si>
+    <t>rmk</t>
+  </si>
+  <si>
+    <t>wol</t>
   </si>
 </sst>
 </file>
@@ -106,7 +118,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -155,6 +167,389 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Additional_LU_and_deforestation"/>
+      <sheetName val="Land_Cover"/>
+      <sheetName val="Land_Cover_MIN_MAX"/>
+      <sheetName val="GTAP_area"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Shocks_GlobalTarf_qxw"/>
+      <sheetName val="Shocks_tmf_f"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Shocks_tmf_f2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7">
+        <row r="41">
+          <cell r="C41">
+            <v>1.1000000000000001</v>
+          </cell>
+          <cell r="D41">
+            <v>1.1000000000000001</v>
+          </cell>
+          <cell r="E41">
+            <v>3</v>
+          </cell>
+          <cell r="F41">
+            <v>1.6</v>
+          </cell>
+          <cell r="G41">
+            <v>3</v>
+          </cell>
+          <cell r="H41">
+            <v>0.4</v>
+          </cell>
+          <cell r="I41">
+            <v>2.6</v>
+          </cell>
+          <cell r="J41">
+            <v>1.2</v>
+          </cell>
+          <cell r="K41">
+            <v>1.4</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>0.9</v>
+          </cell>
+          <cell r="D42">
+            <v>0.7</v>
+          </cell>
+          <cell r="E42">
+            <v>5.5</v>
+          </cell>
+          <cell r="F42">
+            <v>1.3</v>
+          </cell>
+          <cell r="G42">
+            <v>4.8</v>
+          </cell>
+          <cell r="H42">
+            <v>0.4</v>
+          </cell>
+          <cell r="I42">
+            <v>12.9</v>
+          </cell>
+          <cell r="J42">
+            <v>0.7</v>
+          </cell>
+          <cell r="K42">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>0.5</v>
+          </cell>
+          <cell r="D43">
+            <v>4.3</v>
+          </cell>
+          <cell r="E43">
+            <v>2.5</v>
+          </cell>
+          <cell r="F43">
+            <v>1</v>
+          </cell>
+          <cell r="G43">
+            <v>1.3</v>
+          </cell>
+          <cell r="H43">
+            <v>1.8</v>
+          </cell>
+          <cell r="I43">
+            <v>1.6</v>
+          </cell>
+          <cell r="J43">
+            <v>0.8</v>
+          </cell>
+          <cell r="K43">
+            <v>0.8</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>3.3</v>
+          </cell>
+          <cell r="D44">
+            <v>1.4</v>
+          </cell>
+          <cell r="E44">
+            <v>15.7</v>
+          </cell>
+          <cell r="F44">
+            <v>3.7</v>
+          </cell>
+          <cell r="G44">
+            <v>4.2</v>
+          </cell>
+          <cell r="H44">
+            <v>3.9</v>
+          </cell>
+          <cell r="I44">
+            <v>10.199999999999999</v>
+          </cell>
+          <cell r="J44">
+            <v>2.7</v>
+          </cell>
+          <cell r="K44">
+            <v>4.9000000000000004</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>1.9</v>
+          </cell>
+          <cell r="D45">
+            <v>1.5</v>
+          </cell>
+          <cell r="E45">
+            <v>4.0999999999999996</v>
+          </cell>
+          <cell r="F45">
+            <v>3.9</v>
+          </cell>
+          <cell r="G45">
+            <v>6.8</v>
+          </cell>
+          <cell r="H45">
+            <v>2.5</v>
+          </cell>
+          <cell r="I45">
+            <v>2.2000000000000002</v>
+          </cell>
+          <cell r="J45">
+            <v>3.6</v>
+          </cell>
+          <cell r="K45">
+            <v>4.4000000000000004</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>0.6</v>
+          </cell>
+          <cell r="D46">
+            <v>2.9</v>
+          </cell>
+          <cell r="E46">
+            <v>10.9</v>
+          </cell>
+          <cell r="F46">
+            <v>1.2</v>
+          </cell>
+          <cell r="G46">
+            <v>1</v>
+          </cell>
+          <cell r="H46">
+            <v>1</v>
+          </cell>
+          <cell r="I46">
+            <v>0.7</v>
+          </cell>
+          <cell r="J46">
+            <v>1</v>
+          </cell>
+          <cell r="K46">
+            <v>0.3</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="C47">
+            <v>2.2000000000000002</v>
+          </cell>
+          <cell r="D47">
+            <v>2.6</v>
+          </cell>
+          <cell r="E47">
+            <v>3.7</v>
+          </cell>
+          <cell r="F47">
+            <v>6.3</v>
+          </cell>
+          <cell r="G47">
+            <v>5.7</v>
+          </cell>
+          <cell r="H47">
+            <v>6.7</v>
+          </cell>
+          <cell r="I47">
+            <v>9.1</v>
+          </cell>
+          <cell r="J47">
+            <v>6.2</v>
+          </cell>
+          <cell r="K47">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="C48">
+            <v>13.2</v>
+          </cell>
+          <cell r="D48">
+            <v>14.6</v>
+          </cell>
+          <cell r="E48">
+            <v>18.600000000000001</v>
+          </cell>
+          <cell r="F48">
+            <v>27.9</v>
+          </cell>
+          <cell r="G48">
+            <v>20.9</v>
+          </cell>
+          <cell r="H48">
+            <v>15.1</v>
+          </cell>
+          <cell r="I48">
+            <v>21.3</v>
+          </cell>
+          <cell r="J48">
+            <v>22.6</v>
+          </cell>
+          <cell r="K48">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="C49">
+            <v>18.3</v>
+          </cell>
+          <cell r="D49">
+            <v>0.3</v>
+          </cell>
+          <cell r="E49">
+            <v>1.3</v>
+          </cell>
+          <cell r="F49">
+            <v>1</v>
+          </cell>
+          <cell r="G49">
+            <v>2.2999999999999998</v>
+          </cell>
+          <cell r="H49">
+            <v>2</v>
+          </cell>
+          <cell r="I49">
+            <v>17.100000000000001</v>
+          </cell>
+          <cell r="J49">
+            <v>3.6</v>
+          </cell>
+          <cell r="K49">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="C50">
+            <v>3.1</v>
+          </cell>
+          <cell r="D50">
+            <v>2.9</v>
+          </cell>
+          <cell r="E50">
+            <v>18.399999999999999</v>
+          </cell>
+          <cell r="F50">
+            <v>7.3</v>
+          </cell>
+          <cell r="G50">
+            <v>9.1999999999999993</v>
+          </cell>
+          <cell r="H50">
+            <v>24.2</v>
+          </cell>
+          <cell r="I50">
+            <v>12.5</v>
+          </cell>
+          <cell r="J50">
+            <v>5.7</v>
+          </cell>
+          <cell r="K50">
+            <v>5.6</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="C51">
+            <v>2.4</v>
+          </cell>
+          <cell r="D51">
+            <v>3.6</v>
+          </cell>
+          <cell r="E51">
+            <v>5</v>
+          </cell>
+          <cell r="F51">
+            <v>12.3</v>
+          </cell>
+          <cell r="G51">
+            <v>10.7</v>
+          </cell>
+          <cell r="H51">
+            <v>2.8</v>
+          </cell>
+          <cell r="I51">
+            <v>9.5</v>
+          </cell>
+          <cell r="J51">
+            <v>4.7</v>
+          </cell>
+          <cell r="K51">
+            <v>2.8</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="C52">
+            <v>1.2</v>
+          </cell>
+          <cell r="D52">
+            <v>0.8</v>
+          </cell>
+          <cell r="E52">
+            <v>4.5999999999999996</v>
+          </cell>
+          <cell r="F52">
+            <v>14.5</v>
+          </cell>
+          <cell r="G52">
+            <v>9.9</v>
+          </cell>
+          <cell r="H52">
+            <v>2.9</v>
+          </cell>
+          <cell r="I52">
+            <v>15</v>
+          </cell>
+          <cell r="J52">
+            <v>4.5</v>
+          </cell>
+          <cell r="K52">
+            <v>3.7</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -454,10 +849,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F83C31E-1F5F-495B-8648-E82BD436A23B}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,357 +883,599 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1">
-        <v>1.21</v>
+        <f>[1]Shocks_tmf_f!C41</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C2" s="1">
-        <v>1.34</v>
+        <f>[1]Shocks_tmf_f!D41</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D2" s="1">
-        <v>2.9</v>
+        <f>[1]Shocks_tmf_f!E41</f>
+        <v>3</v>
       </c>
       <c r="E2" s="1">
-        <v>1.89</v>
+        <f>[1]Shocks_tmf_f!F41</f>
+        <v>1.6</v>
       </c>
       <c r="F2" s="1">
-        <v>3.17</v>
+        <f>[1]Shocks_tmf_f!G41</f>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0.48</v>
+        <f>[1]Shocks_tmf_f!H41</f>
+        <v>0.4</v>
       </c>
       <c r="H2" s="1">
-        <v>2.97</v>
+        <f>[1]Shocks_tmf_f!I41</f>
+        <v>2.6</v>
       </c>
       <c r="I2" s="1">
-        <v>1.35</v>
+        <f>[1]Shocks_tmf_f!J41</f>
+        <v>1.2</v>
       </c>
       <c r="J2" s="1">
-        <v>0.51</v>
+        <f>[1]Shocks_tmf_f!K41</f>
+        <v>1.4</v>
+      </c>
+      <c r="K2" s="1">
+        <f>C2</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L2" s="1">
+        <f>C2</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1">
-        <v>1.1599999999999999</v>
+        <f>[1]Shocks_tmf_f!C42</f>
+        <v>0.9</v>
       </c>
       <c r="C3" s="1">
-        <v>0.92</v>
+        <f>[1]Shocks_tmf_f!D42</f>
+        <v>0.7</v>
       </c>
       <c r="D3" s="1">
-        <v>4.93</v>
+        <f>[1]Shocks_tmf_f!E42</f>
+        <v>5.5</v>
       </c>
       <c r="E3" s="1">
-        <v>1.78</v>
+        <f>[1]Shocks_tmf_f!F42</f>
+        <v>1.3</v>
       </c>
       <c r="F3" s="1">
-        <v>5.09</v>
+        <f>[1]Shocks_tmf_f!G42</f>
+        <v>4.8</v>
       </c>
       <c r="G3" s="1">
-        <v>0.46</v>
+        <f>[1]Shocks_tmf_f!H42</f>
+        <v>0.4</v>
       </c>
       <c r="H3" s="1">
-        <v>14.22</v>
+        <f>[1]Shocks_tmf_f!I42</f>
+        <v>12.9</v>
       </c>
       <c r="I3" s="1">
-        <v>0.77</v>
+        <f>[1]Shocks_tmf_f!J42</f>
+        <v>0.7</v>
       </c>
       <c r="J3" s="1">
+        <f>[1]Shocks_tmf_f!K42</f>
         <v>0</v>
       </c>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K13" si="0">C3</f>
+        <v>0.7</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L13" si="1">C3</f>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>0.62</v>
+        <f>[1]Shocks_tmf_f!C43</f>
+        <v>0.5</v>
       </c>
       <c r="C4" s="1">
-        <v>0.28999999999999998</v>
+        <f>[1]Shocks_tmf_f!D43</f>
+        <v>4.3</v>
       </c>
       <c r="D4" s="1">
-        <v>1.97</v>
+        <f>[1]Shocks_tmf_f!E43</f>
+        <v>2.5</v>
       </c>
       <c r="E4" s="1">
-        <v>1.1000000000000001</v>
+        <f>[1]Shocks_tmf_f!F43</f>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
-        <v>1.07</v>
+        <f>[1]Shocks_tmf_f!G43</f>
+        <v>1.3</v>
       </c>
       <c r="G4" s="1">
-        <v>0.93</v>
+        <f>[1]Shocks_tmf_f!H43</f>
+        <v>1.8</v>
       </c>
       <c r="H4" s="1">
-        <v>1.82</v>
+        <f>[1]Shocks_tmf_f!I43</f>
+        <v>1.6</v>
       </c>
       <c r="I4" s="1">
-        <v>1.55</v>
+        <f>[1]Shocks_tmf_f!J43</f>
+        <v>0.8</v>
       </c>
       <c r="J4" s="1">
-        <v>0.92</v>
+        <f>[1]Shocks_tmf_f!K43</f>
+        <v>0.8</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="0"/>
+        <v>4.3</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="1"/>
+        <v>4.3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1">
-        <v>2.66</v>
+        <f>[1]Shocks_tmf_f!C44</f>
+        <v>3.3</v>
       </c>
       <c r="C5" s="1">
-        <v>2.15</v>
+        <f>[1]Shocks_tmf_f!D44</f>
+        <v>1.4</v>
       </c>
       <c r="D5" s="1">
-        <v>16.23</v>
+        <f>[1]Shocks_tmf_f!E44</f>
+        <v>15.7</v>
       </c>
       <c r="E5" s="1">
-        <v>7.24</v>
+        <f>[1]Shocks_tmf_f!F44</f>
+        <v>3.7</v>
       </c>
       <c r="F5" s="1">
-        <v>4.37</v>
+        <f>[1]Shocks_tmf_f!G44</f>
+        <v>4.2</v>
       </c>
       <c r="G5" s="1">
-        <v>3.52</v>
+        <f>[1]Shocks_tmf_f!H44</f>
+        <v>3.9</v>
       </c>
       <c r="H5" s="1">
-        <v>6.98</v>
+        <f>[1]Shocks_tmf_f!I44</f>
+        <v>10.199999999999999</v>
       </c>
       <c r="I5" s="1">
-        <v>5.17</v>
+        <f>[1]Shocks_tmf_f!J44</f>
+        <v>2.7</v>
       </c>
       <c r="J5" s="1">
-        <v>4.43</v>
+        <f>[1]Shocks_tmf_f!K44</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="1"/>
+        <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>3.5</v>
+        <f>[1]Shocks_tmf_f!C45</f>
+        <v>1.9</v>
       </c>
       <c r="C6" s="1">
-        <v>1.63</v>
+        <f>[1]Shocks_tmf_f!D45</f>
+        <v>1.5</v>
       </c>
       <c r="D6" s="1">
-        <v>6.29</v>
+        <f>[1]Shocks_tmf_f!E45</f>
+        <v>4.0999999999999996</v>
       </c>
       <c r="E6" s="1">
-        <v>6.56</v>
+        <f>[1]Shocks_tmf_f!F45</f>
+        <v>3.9</v>
       </c>
       <c r="F6" s="1">
-        <v>10.06</v>
+        <f>[1]Shocks_tmf_f!G45</f>
+        <v>6.8</v>
       </c>
       <c r="G6" s="1">
-        <v>3.23</v>
+        <f>[1]Shocks_tmf_f!H45</f>
+        <v>2.5</v>
       </c>
       <c r="H6" s="1">
-        <v>2.96</v>
+        <f>[1]Shocks_tmf_f!I45</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I6" s="1">
+        <f>[1]Shocks_tmf_f!J45</f>
+        <v>3.6</v>
+      </c>
+      <c r="J6" s="1">
+        <f>[1]Shocks_tmf_f!K45</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1">
+        <f>[1]Shocks_tmf_f!C46</f>
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="1">
+        <f>[1]Shocks_tmf_f!D46</f>
+        <v>2.9</v>
+      </c>
+      <c r="D7" s="1">
+        <f>[1]Shocks_tmf_f!E46</f>
+        <v>10.9</v>
+      </c>
+      <c r="E7" s="1">
+        <f>[1]Shocks_tmf_f!F46</f>
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="1">
+        <f>[1]Shocks_tmf_f!G46</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <f>[1]Shocks_tmf_f!H46</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <f>[1]Shocks_tmf_f!I46</f>
+        <v>0.7</v>
+      </c>
+      <c r="I7" s="1">
+        <f>[1]Shocks_tmf_f!J46</f>
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <f>[1]Shocks_tmf_f!K46</f>
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="1"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <f>[1]Shocks_tmf_f!C47</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C8" s="1">
+        <f>[1]Shocks_tmf_f!D47</f>
+        <v>2.6</v>
+      </c>
+      <c r="D8" s="1">
+        <f>[1]Shocks_tmf_f!E47</f>
+        <v>3.7</v>
+      </c>
+      <c r="E8" s="1">
+        <f>[1]Shocks_tmf_f!F47</f>
+        <v>6.3</v>
+      </c>
+      <c r="F8" s="1">
+        <f>[1]Shocks_tmf_f!G47</f>
+        <v>5.7</v>
+      </c>
+      <c r="G8" s="1">
+        <f>[1]Shocks_tmf_f!H47</f>
+        <v>6.7</v>
+      </c>
+      <c r="H8" s="1">
+        <f>[1]Shocks_tmf_f!I47</f>
+        <v>9.1</v>
+      </c>
+      <c r="I8" s="1">
+        <f>[1]Shocks_tmf_f!J47</f>
         <v>6.2</v>
       </c>
-      <c r="J6" s="1">
-        <v>8.23</v>
+      <c r="J8" s="1">
+        <f>[1]Shocks_tmf_f!K47</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1">
+        <f>[1]Shocks_tmf_f!C48</f>
+        <v>13.2</v>
+      </c>
+      <c r="C9" s="1">
+        <f>[1]Shocks_tmf_f!D48</f>
+        <v>14.6</v>
+      </c>
+      <c r="D9" s="1">
+        <f>[1]Shocks_tmf_f!E48</f>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E9" s="1">
+        <f>[1]Shocks_tmf_f!F48</f>
+        <v>27.9</v>
+      </c>
+      <c r="F9" s="1">
+        <f>[1]Shocks_tmf_f!G48</f>
+        <v>20.9</v>
+      </c>
+      <c r="G9" s="1">
+        <f>[1]Shocks_tmf_f!H48</f>
+        <v>15.1</v>
+      </c>
+      <c r="H9" s="1">
+        <f>[1]Shocks_tmf_f!I48</f>
+        <v>21.3</v>
+      </c>
+      <c r="I9" s="1">
+        <f>[1]Shocks_tmf_f!J48</f>
+        <v>22.6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>[1]Shocks_tmf_f!K48</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>14.6</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="1"/>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1">
+        <f>[1]Shocks_tmf_f!C49</f>
+        <v>18.3</v>
+      </c>
+      <c r="C10" s="1">
+        <f>[1]Shocks_tmf_f!D49</f>
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="1">
+        <f>[1]Shocks_tmf_f!E49</f>
+        <v>1.3</v>
+      </c>
+      <c r="E10" s="1">
+        <f>[1]Shocks_tmf_f!F49</f>
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <f>[1]Shocks_tmf_f!G49</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G10" s="1">
+        <f>[1]Shocks_tmf_f!H49</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="1">
+        <f>[1]Shocks_tmf_f!I49</f>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="I10" s="1">
+        <f>[1]Shocks_tmf_f!J49</f>
+        <v>3.6</v>
+      </c>
+      <c r="J10" s="1">
+        <f>[1]Shocks_tmf_f!K49</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1">
+        <f>[1]Shocks_tmf_f!C50</f>
+        <v>3.1</v>
+      </c>
+      <c r="C11" s="1">
+        <f>[1]Shocks_tmf_f!D50</f>
+        <v>2.9</v>
+      </c>
+      <c r="D11" s="1">
+        <f>[1]Shocks_tmf_f!E50</f>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E11" s="1">
+        <f>[1]Shocks_tmf_f!F50</f>
+        <v>7.3</v>
+      </c>
+      <c r="F11" s="1">
+        <f>[1]Shocks_tmf_f!G50</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G11" s="1">
+        <f>[1]Shocks_tmf_f!H50</f>
+        <v>24.2</v>
+      </c>
+      <c r="H11" s="1">
+        <f>[1]Shocks_tmf_f!I50</f>
+        <v>12.5</v>
+      </c>
+      <c r="I11" s="1">
+        <f>[1]Shocks_tmf_f!J50</f>
+        <v>5.7</v>
+      </c>
+      <c r="J11" s="1">
+        <f>[1]Shocks_tmf_f!K50</f>
+        <v>5.6</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="1"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1">
+        <f>[1]Shocks_tmf_f!C51</f>
+        <v>2.4</v>
+      </c>
+      <c r="C12" s="1">
+        <f>[1]Shocks_tmf_f!D51</f>
+        <v>3.6</v>
+      </c>
+      <c r="D12" s="1">
+        <f>[1]Shocks_tmf_f!E51</f>
+        <v>5</v>
+      </c>
+      <c r="E12" s="1">
+        <f>[1]Shocks_tmf_f!F51</f>
+        <v>12.3</v>
+      </c>
+      <c r="F12" s="1">
+        <f>[1]Shocks_tmf_f!G51</f>
+        <v>10.7</v>
+      </c>
+      <c r="G12" s="1">
+        <f>[1]Shocks_tmf_f!H51</f>
+        <v>2.8</v>
+      </c>
+      <c r="H12" s="1">
+        <f>[1]Shocks_tmf_f!I51</f>
+        <v>9.5</v>
+      </c>
+      <c r="I12" s="1">
+        <f>[1]Shocks_tmf_f!J51</f>
+        <v>4.7</v>
+      </c>
+      <c r="J12" s="1">
+        <f>[1]Shocks_tmf_f!K51</f>
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="1"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1">
+        <f>[1]Shocks_tmf_f!C52</f>
+        <v>1.2</v>
+      </c>
+      <c r="C13" s="1">
+        <f>[1]Shocks_tmf_f!D52</f>
+        <v>0.8</v>
+      </c>
+      <c r="D13" s="1">
+        <f>[1]Shocks_tmf_f!E52</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E13" s="1">
+        <f>[1]Shocks_tmf_f!F52</f>
+        <v>14.5</v>
+      </c>
+      <c r="F13" s="1">
+        <f>[1]Shocks_tmf_f!G52</f>
+        <v>9.9</v>
+      </c>
+      <c r="G13" s="1">
+        <f>[1]Shocks_tmf_f!H52</f>
+        <v>2.9</v>
+      </c>
+      <c r="H13" s="1">
+        <f>[1]Shocks_tmf_f!I52</f>
         <v>15</v>
       </c>
-      <c r="B7" s="1">
-        <v>1.26</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="D7" s="1">
-        <v>8.98</v>
-      </c>
-      <c r="E7" s="1">
-        <v>4.87</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2.66</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1.21</v>
-      </c>
-      <c r="I7" s="1">
-        <v>3.48</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2.37</v>
-      </c>
-      <c r="E8" s="1">
-        <v>2.85</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2.9</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2.56</v>
-      </c>
-      <c r="H8" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="I8" s="1">
-        <v>3.15</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1">
-        <v>11.29</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6.98</v>
-      </c>
-      <c r="D9" s="1">
-        <v>12.35</v>
-      </c>
-      <c r="E9" s="1">
-        <v>24.36</v>
-      </c>
-      <c r="F9" s="1">
-        <v>14.14</v>
-      </c>
-      <c r="G9" s="1">
-        <v>9.99</v>
-      </c>
-      <c r="H9" s="1">
-        <v>18.579999999999998</v>
-      </c>
-      <c r="I9" s="1">
-        <v>21.3</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>24.97</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="D10" s="1">
-        <v>6.86</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.97</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2.19</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.93</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7.98</v>
-      </c>
-      <c r="I10" s="1">
-        <v>4.24</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3.91</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="D11" s="1">
-        <v>19.14</v>
-      </c>
-      <c r="E11" s="1">
-        <v>6.37</v>
-      </c>
-      <c r="F11" s="1">
-        <v>6.01</v>
-      </c>
-      <c r="G11" s="1">
-        <v>17.59</v>
-      </c>
-      <c r="H11" s="1">
-        <v>16.010000000000002</v>
-      </c>
-      <c r="I11" s="1">
-        <v>4.03</v>
-      </c>
-      <c r="J11" s="1">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1">
-        <v>6.01</v>
-      </c>
-      <c r="C12" s="1">
-        <v>4.93</v>
-      </c>
-      <c r="D12" s="1">
-        <v>10.4</v>
-      </c>
-      <c r="E12" s="1">
-        <v>14.73</v>
-      </c>
-      <c r="F12" s="1">
-        <v>32.450000000000003</v>
-      </c>
-      <c r="G12" s="1">
-        <v>6.43</v>
-      </c>
-      <c r="H12" s="1">
-        <v>27.36</v>
-      </c>
-      <c r="I12" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="J12" s="1">
-        <v>3.97</v>
+      <c r="I13" s="1">
+        <f>[1]Shocks_tmf_f!J52</f>
+        <v>4.5</v>
+      </c>
+      <c r="J13" s="1">
+        <f>[1]Shocks_tmf_f!K52</f>
+        <v>3.7</v>
+      </c>
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
